--- a/artifacts/correct_responses/qwen14b_rag_kimi_judge/all_runs_single_sheet.xlsx
+++ b/artifacts/correct_responses/qwen14b_rag_kimi_judge/all_runs_single_sheet.xlsx
@@ -543,7 +543,6 @@
 Hyundai Transys Georgia Powertrain | Thermal Management | Electrical heaters, control units, and actuators
 Hyundai Transys Georgia Seating Systems | General Automotive | Automotive electronics, resonators, capacitors, resistors, electronics and electronic parts
 IMMI | Battery Pack | Battery electrolyte
-IMS Gear Georgia Inc. | General Automotive | Car audio systems
 Inalfa Roof Systems Inc. | General Automotive | Automotive electronic safety systems
 JAC Products Inc. | General Automotive | Switches, resistors and related products
 Jefferson Southern Corp. | General Automotive | High current switches and resistors for automotive HVAC systems
@@ -560,7 +559,8 @@
 Lund International Inc. | General Automotive | Automotive seat frames
 Lund International Inc./Ventshade Division | General Automotive | Industrial trailers and truck bodies
 Lyle Industries Inc. | General Automotive | Automatic transmissions
-Lyle Industries Inc. | General Automotive | Molded injection auto parts</t>
+Lyle Industries Inc. | General Automotive | Molded injection auto parts
+Mack Trucks | General Automotive | Interior and exterior automotive components</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0556</v>
+        <v>0.1111</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>32.0523076923077</v>
+        <v>33.33307692307692</v>
       </c>
     </row>
     <row r="3">
@@ -611,12 +611,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>F&amp;P Georgia Manufacturing | Tier 1/2 | Battery Pack  
-Hitachi Astemo Americas Inc. | Tier 1/2 | Battery Cell  
-Hollingsworth &amp; Vose Co. | Tier 1/2 | Battery Pack  
-Honda Development &amp; Manufacturing | Tier 1/2 | Battery Cell  
-Hyundai Motor Group | Tier 1/2 | Battery Pack  
-IMMI | Tier 1/2 | Battery Pack</t>
+          <t>F&amp;P Georgia Manufacturing - Battery Pack - Tier 1/2  
+Hitachi Astemo Americas Inc. - Battery Cell - Tier 1/2  
+Hollingsworth &amp; Vose Co. - Battery Pack - Tier 1/2  
+Honda Development &amp; Manufacturing - Battery Cell - Tier 1/2  
+Hyundai Motor Group - Battery Pack - Tier 1/2  
+IMMI - Battery Pack - Tier 1/2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No Thermal Management suppliers and their linked Primary OEMs were provided in the given evidence. The evidence lists companies involved in General Automotive roles but does not specify any with a Thermal Management role.</t>
+          <t>No Thermal Management suppliers were found in Georgia based on the provided evidence. All listed companies have an EV Supply Chain Role of General Automotive or no specific relevance to thermal management systems.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -714,34 +714,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GSC Steel Stamping LLC | Power Electronics | Employment: 350
-Morgan Corp. | Charging Infrastructure | Employment: 320
-Yazaki North America | Power electronics, sensors, and EV systems | Employment: 230000
-ZF Gainesville LLC | EV thermal management and power electronics | Employment: 17500</t>
+          <t>**Power Electronics**
+- GSC Steel Stamping LLC | Employment: 350
+- Yazaki North America | Employment: 230000
+- ZF Gainesville LLC | Employment: 17500
+**Charging Infrastructure**
+- (No companies found in the provided evidence)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>76.92307692307692</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="6">
@@ -773,11 +775,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Vehicle Assembly:
-Superior Essex Inc. | Vehicle Assembly
-TE Connectivity | Vehicle Assembly
-Teklas USA | Vehicle Assembly
-Thomson Plastics Inc. | Vehicle Assembly</t>
+          <t>The provided evidence does not include any companies classified as Direct Manufacturer or specify their EV Supply Chain Roles. The data focuses on other categories such as Tier 1, OEM Footprint, and OEM Supply Chain but does not mention Direct Manufacturer explicitly. Therefore, there is no information to provide for the requested classification of Direct Manufacturers and their associated roles from the given evidence.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -786,10 +784,10 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.3833</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -801,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>22.30692307692307</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="7">
@@ -832,7 +830,7 @@
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
@@ -842,16 +840,16 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>53.84615384615385</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="8">
@@ -882,7 +880,7 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -897,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>30.76923076923077</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="9">
@@ -923,26 +921,26 @@
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="10">
@@ -963,12 +961,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cobb County has the highest total employment across all companies, with a combined employment of 10,000 (TE Connectivity: 1900 and Superior Essex Inc.: 8100).</t>
+          <t>Statewide / Unspecified has the highest total employment across all companies with an employment total of 1354440.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
@@ -978,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.84615384615385</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="11">
@@ -1024,15 +1022,51 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>Vehicle Assembly OEMs in Georgia and their Tier 1 suppliers connected within the state:
-No specific Vehicle Assembly OEMs are listed in the provided evidence. However, the following Tier 1 suppliers are mentioned as part of the automotive supply chain participant network in Georgia:
-- Jefferson Southern Corporation | Category: Tier 1 | EV Supply Chain Role: General Automotive | Location: Commerce, Forsyth County | Employment: 900
-- Joon Georgia, Inc. | Category: Tier 1 | EV Supply Chain Role: General Automotive | Location: Commerce, Forsyth County | Employment: 900
-- JTEKT North America Corp. | Category: Tier 1 | EV Supply Chain Role: General Automotive | Location: Warrenton, Warren County | Employment: 860
-- Kautex Inc. | Category: Tier 1 | EV Supply Chain Role: General Automotive | Location: Lagrange, Troup County | Employment: 800
-- KTX America Corporation | Category: Tier 1 | EV Supply Chain Role: General Automotive | Location: West Point, Troup County | Employment: 740
-- Kumho Tire USA Inc. | Category: Tier 1 | EV Supply Chain Role: General Automotive | Location: Macon, Bibb County | Employment: 730
-- Kyungshin America Corp. | Category: Tier 1 | EV Supply Chain Role: General Automotive | Location: West Point, Troup County | Employment: 700
-Note: The evidence does not specify any Vehicle Assembly OEMs in Georgia.</t>
+**Vehicle Assembly OEMs:**
+No specific Vehicle Assembly OEMs are listed in the provided evidence. The list includes only Tier 1 suppliers without specifying any vehicle assembly OEMs directly.
+**Tier 1 Suppliers:**
+- **Jefferson Southern Corporation**
+  - Category: Tier 1
+  - Industry Group: Transportation Equipment
+  - EV Supply Chain Role: General Automotive
+  - Primary Facility Type: Manufacturing Plant
+  - Employment: 900
+- **Joon Georgia, Inc.**
+  - Category: Tier 1
+  - Industry Group: Transportation Equipment
+  - EV Supply Chain Role: General Automotive
+  - Primary Facility Type: Manufacturing Plant
+  - Employment: 900
+- **JTEKT North America Corp.**
+  - Category: Tier 1
+  - Industry Group: Transportation Equipment
+  - EV Supply Chain Role: General Automotive
+  - Primary Facility Type: Manufacturing Plant
+  - Employment: 860
+- **Kautex Inc.**
+  - Category: Tier 1
+  - Industry Group: Transportation Equipment
+  - EV Supply Chain Role: General Automotive
+  - Primary Facility Type: Manufacturing Plant
+  - Employment: 800
+- **KTX America Corporation**
+  - Category: Tier 1
+  - Industry Group: Transportation Equipment
+  - EV Supply Chain Role: General Automotive
+  - Primary Facility Type: Manufacturing Plant
+  - Employment: 740
+- **Kumho Tire USA Inc.**
+  - Category: Tier 1
+  - Industry Group: Transportation Equipment
+  - EV Supply Chain Role: General Automotive
+  - Primary Facility Type: Manufacturing Plant
+  - Employment: 730
+- **Kyungshin America Corp.**
+  - Category: Tier 1
+  - Industry Group: Transportation Equipment
+  - EV Supply Chain Role: General Automotive
+  - Primary Facility Type: Manufacturing Plant
+  - Employment: 700</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -1080,32 +1114,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Primary Facility Type: Manufacturing Plant | Product / Service: Motor vehicle engines and parts | Location: Peachtree City, Chattooga County | Employment: 75 | EV / Battery Relevant: Indirect
-Primary Facility Type: Manufacturing Plant | Product / Service: Fire truck bodies | Location: West Point, Troup County | Employment: 75 | EV / Battery Relevant: No</t>
+          <t>Primary products and services associated with Sewon America Inc. across its different operational sites in Georgia:
+- Motor vehicle engines and parts | Location: Peachtree City, Chattooga County | Employment: 75 | EV / Battery Relevant: Indirect | Primary Facility Type: Manufacturing Plant
+- Fire truck bodies | Location: West Point, Troup County | Employment: 75 | EV / Battery Relevant: No | Primary Facility Type: Manufacturing Plant</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>59.61538461538461</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="13">
@@ -1129,8 +1164,8 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ACM Georgia LLC | Category: Tier 2/3 | Industry Group: Textile Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 400 | EV / Battery Relevant: Indirect
-Adient | Category: Tier 2/3 | Industry Group: Textile Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 180 | EV / Battery Relevant: Indirect</t>
+          <t>Company: ACM Georgia LLC | Category: Tier 2/3 | Industry Group: Textile Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 400 | EV / Battery Relevant: Indirect
+Company: Adient | Category: Tier 2/3 | Industry Group: Textile Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 180 | EV / Battery Relevant: Indirect</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -1180,15 +1215,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tier 1:
-- Rivian Automotive | EV Supply Chain Role: General Automotive
-Tier 2/3:
-- Duckyang | EV Supply Chain Role: General Automotive
-- Enchem America Inc. | EV Supply Chain Role: General Automotive
-Vehicle Assembly (OEM):
-- Suzuki Manufacturing of America Corp. | EV Supply Chain Role: Vehicle Assembly
-Thermal Management:
-- Hyundai Transys Georgia Powertrain | EV Supply Chain Role: Thermal Management</t>
+          <t>**Tier 1**
+- **Vehicle Assembly**
+  - Suzuki Manufacturing of America Corp. | Primary Facility Type: Manufacturing Plant | Employment: 7500 | EV / Battery Relevant: Yes
+- **General Automotive**
+  - Racemark International LLC | Primary Facility Type: R&amp;D | Employment: 120 | EV / Battery Relevant: Yes
+  - Hyundai Transys Georgia Seating Systems | Primary Facility Type: Manufacturing Plant | Employment: 110 | EV / Battery Relevant: Indirect
+- **Thermal Management**
+  - Hyundai Transys Georgia Powertrain | Primary Facility Type: Manufacturing Plant | Employment: 130 | EV / Battery Relevant: Yes
+**Tier 2/3**
+- **General Automotive**
+  - GEDIA Georgia LLC | Primary Facility Type: Manufacturing Plant | Employment: 100 | EV / Battery Relevant: Indirect
+  - Duckyang | Primary Facility Type: Manufacturing Plant | Employment: 250 | EV / Battery Relevant: Yes</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1239,7 +1277,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>No Georgia companies produce battery materials such as anodes, cathodes, electrolytes, or copper foil according to the provided evidence. All listed companies have an EV Supply Chain Role of Materials and their products do not include battery-specific components.</t>
+          <t>No Georgia companies produce battery materials such as anodes, cathodes, electrolytes, or copper foil according to the provided evidence. All listed companies have an EV Supply Chain Role of "Materials" but do not specify involvement with battery-specific components like anodes, cathodes, electrolytes, or copper foil in their product/service descriptions.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1286,8 +1324,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WIKA USA | HV and LV wiring harnesses for EVs and ICE vehicles | Primary OEMs: Yes  
-Woodbridge Foam Corp. | EV wiring harnesses and power distribution | Primary OEMs: Yes</t>
+          <t>No companies in Georgia have an EV Supply Chain Role related to wiring harnesses according to the provided evidence. The roles listed are either "General Automotive" or "Materials".</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1338,7 +1375,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>No Georgia-based Tier 1 or Tier 1/2 suppliers capable of producing battery electrolytes or lithium-ion battery materials with existing OEM contracts were found in the provided evidence.</t>
+          <t>No companies found in the provided evidence match the criteria of being Georgia-based Tier 1 or Tier 1/2 suppliers capable of producing battery electrolytes or lithium-ion battery materials with existing OEM contracts. The listed companies either do not produce these specific materials or their product/service details are not specified to include battery electrolytes or lithium-ion battery materials.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1385,9 +1422,8 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yachiyo Manufacturing of America LLC | Category: OEM Supply Chain | Industry Group: Automotive seating and E‑systems | EV Supply Chain Role: EV electrical distribution and interior systems | Product / Service: Automotive seating and E-Systems (electrical distribution) | Location: Marietta, Cobb County | Primary Facility Type: Manufacturing | Employment: 173700
-WIKA USA | Category: OEM Supply Chain | EV Supply Chain Role: HV and LV wiring harnesses for EVs and ICE vehicles | Updated Location: Georgia | Employment: 250000
-Woodbridge Foam Corp. | Category: OEM Supply Chain | EV Supply Chain Role: EV wiring harnesses and power distribution | Updated Location: Georgia | Employment: 1657</t>
+          <t>WIKA USA | Category: OEM Supply Chain | EV Supply Chain Role: HV and LV wiring harnesses for EVs and ICE vehicles | Location: Georgia | Employment: 250000
+Yachiyo Manufacturing of America LLC | Category: OEM Supply Chain | EV Supply Chain Role: EV electrical distribution and interior systems | Location: Marietta, Cobb County | Primary Facility Type: Manufacturing | Employment: 173700</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1432,8 +1468,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hyundai Transys Georgia Seating Systems | Tier 2/3 | Electronic and Other Electrical Equipment and Components | Power Electronics | Manufacturing Plant | 0 | Gainesville, Hall County | Automotive supply chain participant
-Hyundai Transys Georgia Powertrain | Tier 2/3 | Electronic and Other Electrical Equipment and Components | Power Electronics | Manufacturing Plant | 0 | Gainesville, Hall County | Automotive supply chain participant</t>
+          <t>GSC Steel Stamping LLC | Category: Tier 2/3 | Industry Group: Machinery Except Electrical | EV Supply Chain Role: Power Electronics | Primary Facility Type: Manufacturing Plant | Employment: 350 | Location: Gainesville, Hall County | Primary OEMs: Hyundai Kia Rivian</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1479,12 +1514,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No Georgia-based companies manufacturing copper foil or electrodeposited materials suitable for EV battery current collectors were found in the provided evidence.</t>
+          <t>No Georgia-based companies were found in the provided evidence that manufacture copper foil or electrodeposited materials suitable for EV battery current collectors. All listed companies deal with rubber and miscellaneous plastic products and do not match the specified criteria.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
@@ -1494,16 +1529,16 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>53.84615384615385</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="21">
@@ -1524,8 +1559,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Company: Panasonic Automotive Systems Co. | Category: Tier 1 | Industry Group: Transportation Equipment | EV Supply Chain Role: Materials | Primary Facility Type: Manufacturing Plant | Employment: 175 | Location: Morrow, Clayton County
-Company: PHA Body Systems LLC | Category: Tier 1 | Industry Group: Transportation Equipment | EV Supply Chain Role: Materials | Primary Facility Type: Manufacturing Plant | Employment: 145 | Location: Flowery Branch, Hall County
+          <t>Company: PHA Body Systems LLC | Category: Tier 1 | Industry Group: Transportation Equipment | EV Supply Chain Role: Materials | Primary Facility Type: Manufacturing Plant | Employment: 145 | Location: Flowery Branch, Hall County
 Company: SK Battery America | Category: Tier 1 | Industry Group: Transportation Equipment | EV Supply Chain Role: Materials | Primary Facility Type: Manufacturing Plant | Employment: 75 | Location: Lagrange, Troup County</t>
         </is>
       </c>
@@ -1583,14 +1617,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Battery Cell:
-- Hitachi Astemo Americas Inc., Shorter, Manufacturing Plant, 723 employees
-- Honda Development &amp; Manufacturing, Tallapoosa, Cherokee County, Manufacturing Plant, 400 employees
-Battery Pack:
-- F&amp;P Georgia Manufacturing, Rome, Floyd County, Manufacturing Plant, 104 employees
-- Hollingsworth &amp; Vose Co., Hawkinsville, Pulaski County, Manufacturing Plant, 400 employees
-- Hyundai Motor Group, Ellabell, Bryan County, Manufacturing Plant, 164 employees
-- IMMI, Dublin, Laurens County, Manufacturing Plant, 100 employees</t>
+          <t>Battery Pack Suppliers:
+- F&amp;P Georgia Manufacturing | Location: Rome, Floyd County | Employment: 104
+- Hitachi Astemo Americas Inc. | Location: Shorter | Employment: 723
+- Hollingsworth &amp; Vose Co. | Location: Hawkinsville, Pulaski County | Employment: 400
+- Hyundai Motor Group | Location: Ellabell, Bryan County | Employment: 164
+- IMMI | Location: Dublin, Laurens County | Employment: 100
+Battery Cell Suppliers:
+- Honda Development &amp; Manufacturing | Location: Tallapoosa, Cherokee County | Employment: 400</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1599,10 +1633,10 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4615</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1614,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>41.41923076923077</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="23">
@@ -1638,15 +1672,9 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>**DC-to-DC Converters and Power Electronics Components Relevant to EV Drivetrains**
-1. **GSC Steel Stamping LLC**
-   - Tier: Tier 2/3
-   - Product / Service: DC-to-DC converters
-   - Employment: 350
-2. **ZF Gainesville LLC**
-   - Tier: OEM Supply Chain
-   - EV Supply Chain Role: Power electronics
-   - Employment: 17500</t>
+          <t>GSC Steel Stamping LLC | Tier 2/3 | DC-to-DC converters | Gainesville, Hall County | Manufacturing Plant | 350
+ZF Gainesville LLC | OEM Supply Chain | Power Electronics | Gainesville, Hall County | Manufacturing | 17500
+Yazaki North America | OEM Footprint | Power electronics | Newnan, Coweta County | Engineering / Operations | 230000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1692,7 +1720,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TCI Powder Coatings | Category: OEM | Updated Location: Troup County | Employment: 3000</t>
+          <t>No Georgia companies provide powder coating-related products or services based on the provided evidence.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1743,7 +1771,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hyundai Motor Group | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: Battery Pack | Primary OEMs: Hyundai Kia | Product / Service: Battery parts for electric vehicles | Location: Ellabell, Bryan County | Primary Facility Type: Manufacturing Plant | Employment: 164 | EV / Battery Relevant: Yes | Supplier or Affiliation Type: Automotive supply chain participant | Classification Method: Supplier</t>
+          <t>No Georgia companies in the provided evidence manufacture battery parts or enclosure systems and are classified as Tier 1/2, making them ready for direct OEM engagement. All listed companies are categorized as Tier 2/3 and their EV Supply Chain Role is "General Automotive". The Primary OEMs linked to these companies include Multiple OEMs, Hyundai Kia Rivian, Blue Bird, and Hyundai Kia.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1752,7 +1780,7 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1767,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>15.38384615384615</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="26">
@@ -1798,7 +1826,7 @@
         <is>
           <t>Company: Arising Industries Inc. | Employment: 582 | Location: Covington, Henry County | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: Indirect | Supplier or Affiliation Type: Automotive supply chain participant
 Company: Flambeau Inc. | Employment: 700 | Location: Adairsville, Bartow County | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: No | Supplier or Affiliation Type: Automotive supply chain participant
-Company: Fouts Brothers Fire Equipment | Employment: 630 | Location: Rome, Floyd County | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: Indirect | Supplier or Affiliation Type: Automotive supply chain participant
+Company: Fouts Brothers Fire Equipment | Employment: 630 | Location: Ringgold, Catoosa County | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: Indirect | Supplier or Affiliation Type: Automotive supply chain participant
 Company: Grudem | Employment: 807 | Location: Adairsville, Bartow County | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: No | Supplier or Affiliation Type: Automotive supply chain participant</t>
         </is>
       </c>
@@ -1846,7 +1874,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Archer Aviation Inc. | Category: Tier 2/3 | Industry Group: Chemicals and Allied Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: n/a</t>
+          <t>Company: Arising Industries Inc. | Category: Tier 2/3 | Industry Group: Chemicals and Allied Products | EV Supply Chain Role: General Automotive | Product / Service: N/A | Location: West Point, Chattahoochee County | Primary Facility Type: Manufacturing Plant | Employment: 100 | EV / Battery Relevant: No | Supplier or Affiliation Type: Automotive supply chain participant | Classification Method: Supplier</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1855,10 +1883,10 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1870,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>38.46076923076923</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="28">
@@ -1919,10 +1947,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EV Supply Chain Role: Materials
-Company: Blue Bird Corp.
-EV Supply Chain Role: Materials
-Company: Bosch (Automotive Division)</t>
+          <t>Materials:
+- Aspen Aerogels
+- Aurubis
+- Beaver Manufacturing Co. Inc.
+- Blue Ridge Manufacturing
+- Boogook Industries
+- DAEHAN Solution Georgia LLC
+- Daesol Ausys
+- EVCO Plastics
+Battery Pack:
+- F&amp;P Georgia Manufacturing</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1988,7 +2023,7 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2003,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>30.76923076923077</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="30">
@@ -2030,12 +2065,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>The provided evidence does not contain information about the number of employees for Hyundai Metaplant's Georgia-based EV component suppliers or their capacity fragility. The evidence lists companies and their locations but lacks employee count data necessary to determine potential capacity fragility based on workforce size. Therefore, it is incomplete for answering this specific question.</t>
+          <t>The evidence provided does not contain information about the number of employees for each supplier or their capacity fragility status. Therefore, it's impossible to determine how many Georgia-based EV component suppliers have fewer than 200 employees based on the given data. The workbook only lists cities and counts of locations within those cities but lacks employee count details.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
@@ -2045,16 +2080,16 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>53.84615384615385</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="31">
@@ -2077,7 +2112,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>No companies match the criteria of being Georgia Tier 2/3 suppliers, classified as General Automotive, and providing materials to Battery Cell or Battery Pack companies. All listed companies have an EV Supply Chain Role of "General Automotive" but do not indicate any direct relevance to battery cell or pack manufacturing in their provided details.</t>
+          <t>Based on the provided evidence, there are no Georgia Tier 2/3 suppliers classified as General Automotive that provide materials to Battery Cell or Battery Pack companies and are EV Relevant. All listed companies under the criteria of being General Automotive have an "EV / Battery Relevant" status marked as either Indirect or No, indicating no direct supply chain misalignment risk with Battery Cell or Battery Pack manufacturers.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -2133,13 +2168,15 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Company: Fouts Brothers Fire Equipment | Category: Tier 1/2 | Industry Group: Fabricated Metal Products | EV Supply Chain Role: General Automotive | Primary OEMs: Multiple OEMs | Location: Norcross, Gwinnett County | Primary Facility Type: Manufacturing Plant | Employment: 630 | EV / Battery Relevant: Indirect
-Company: Hitachi Astemo | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary OEMs: Multiple OEMs | Location: Shorter | Primary Facility Type: Manufacturing Plant | Employment: 800 | EV / Battery Relevant: No
-Company: Hwashin | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary OEMs: Multiple OEMs | Location: Lagrange, Haralson County | Primary Facility Type: Manufacturing Plant | Employment: 285 | EV / Battery Relevant: No
-Company: Hyundai &amp; LG Energy Solution (LGES) | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary OEMs: Multiple OEMs | Location: Ellabell | Primary Facility Type: Manufacturing Plant | Employment: 250 | EV / Battery Relevant: No
-Company: Hyundai Industrial Co. | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary OEMs: Multiple OEMs | Location: Pendergrass, Jackson County | Primary Facility Type: Manufacturing Plant | Employment: 182 | EV / Battery Relevant: Indirect
-Company: Hyundai MOBIS (Georgia) | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary OEMs: Multiple OEMs | Location: Lagrange, Meriwether County | Primary Facility Type: Manufacturing Plant | Employment: 170 | EV / Battery Relevant: Indirect
-Company: Hyundai Transys Georgia Seating Systems | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary OEMs: Multiple OEMs | Location: Rome, Floyd County | Primary Facility Type: Manufacturing Plant | Employment: 110 | EV / Battery Relevant: Indirect</t>
+          <t>77 companies match the criteria of being Georgia-based Tier 1/2 automotive suppliers serving 'Multiple OEMs':
+- Fouts Brothers Fire Equipment | Category: Tier 1/2 | Industry Group: Fabricated Metal Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 630
+- Hitachi Astemo | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 800
+- Hwashin | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 285
+- Hyundai &amp; LG Energy Solution (LGES) | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 250
+- Hyundai Industrial Co. | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 182
+- Hyundai MOBIS (Georgia) | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 170
+- Hyundai Transys Georgia Seating Systems | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 110
+(Note: The full list includes all 77 companies matching the criteria as stated in the structured match summary.)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2148,7 +2185,7 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -2163,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>30.76923076923077</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="33">
@@ -2187,11 +2224,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thermal Management:
-- Freudenberg-NOK | Employment: 160 | Location: Lagrange, Troup County | Primary Facility Type: Manufacturing Plant
-- Hyundai Transys Georgia Powertrain | Employment: 130 | Location: West Point, Troup County | Primary Facility Type: Manufacturing Plant
-Power Electronics:
-- GSC Steel Stamping LLC | Employment: 350 | Location: Gainesville, Hall County | Primary Facility Type: Manufacturing Plant</t>
+          <t>**Thermal Management**
+- Company: Freudenberg-NOK | Location: Lagrange, Troup County | Employment: 160
+- Company: Hyundai Transys Georgia Powertrain | Location: West Point, Troup County | Employment: 130
+**Power Electronics**
+- Company: GSC Steel Stamping LLC | Location: Gainesville, Hall County | Employment: 350</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2261,15 +2298,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>**OEM Footprint**
-- TN Americas Holding Inc.: OEM parent group footprint (EV + HD electrification) | Employment: 19600
-- Toyota Industries Group (TACG-TICA): OEM parent group footprint (electric truck strategy) | Employment: 18100
-- YKK USA Inc.: EV sensors, braking, and control systems | Employment: 190159
-**OEM Supply Chain**
-- SungEel Recycling Park Georgia: Materials | Primary OEMs: Multiple OEMs | Employment: Not specified
-- TI Fluid Systems: Vehicle safety systems OEM (EV + ICE) | Employment: 80
-- Valeo: Tier 1 automotive components | Employment: 269
-- Vernay: Stamped and welded assemblies for OEMs | Employment: 1600</t>
+          <t>No companies classified as OEM Footprint or OEM Supply Chain were identified in the provided evidence. All listed companies are categorized under EV Supply Chain Role: General Automotive.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2324,10 +2353,18 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Based on the provided evidence, there are no companies listed as supplying both General Automotive and EV-specific components with employment size data. The list includes companies involved only in General Automotive roles:
-1. ACM Georgia LLC | Employment: 400
-2. Adient | Employment: 180
-The remaining companies either do not have sufficient information or are categorized solely under the General Automotive role without specific EV transition readiness details provided in this evidence set.</t>
+          <t>Based on the provided evidence, there are no companies listed as supplying both General Automotive and EV-specific components. All companies listed under "General Automotive" role do not specify involvement with EV-specific components. Therefore, it is not possible to provide a list of top 10 Georgia companies based on employment size that supply both General Automotive and EV-specific components indicating transition readiness from the given data.
+Top 10 by Employment Size in General Automotive Role:
+- Arising Industries Inc.: 582
+- Flambeau Inc.: 700
+- Fouts Brothers Fire Equipment: 630
+- Grudem: 807
+- Hitachi Astemo: 800
+- Kautex Inc.: 800
+- Kyungshin America Corp.: 700
+- Lark United Manufacturing Inc.: 700
+- Lear Corporation: 590
+- Lehigh Technologies Inc.: 520</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2372,10 +2409,10 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>No Georgia companies are producing lithium-ion battery materials, cells, or electrolytes according to the provided evidence. The listed companies are involved in traditional ICE powertrain components and related materials. 
-Companies involved in traditional ICE powertrain components:
-- Ascend Elements | EV Supply Chain Role: Materials | Location: Norcross, Gwinnett County
-- Aspen Aerogels | EV Supply Chain Role: Materials | Location: Covington, Henry County</t>
+          <t>No Georgia companies are producing lithium-ion battery materials, cells, or electrolytes according to the provided evidence. There are 22 companies listed with roles related to ICE powertrain components and materials. 
+Companies involved in ICE powertrain components and materials:
+- Ascend Elements | EV Supply Chain Role: Materials
+- Aspen Aerogels | EV Supply Chain Role: Materials</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2473,8 +2510,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Woory Industrial Co. | Category: OEM Supply Chain | EV Supply Chain Role: High‑voltage EV connectors and electronics | Updated Location: Georgia | Employment: 87000
-ZF Gainesville LLC | Category: OEM Supply Chain | EV Supply Chain Role: EV thermal management and power electronics | Updated Location: Georgia | Employment: 17500</t>
+          <t>No companies in Georgia match the criteria of having product descriptions including 'high-voltage', 'DC-to-DC', 'inverter', or 'motor controller'. All provided entries describe products related to automotive textiles and floor coverings, which do not align with EV powertrain electronics.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2522,7 +2558,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TN Americas Holding Inc. | Category: OEM (Footprint) | EV Supply Chain Role: OEM parent group footprint (EV + HD electrification) | Updated Location: Georgia | Employment: 19600</t>
+          <t>No Georgia automotive companies employ over 1,000 workers but are currently categorized as only "Indirectly Relevant" to the EV sector based on the provided evidence. The largest company listed with indirect relevance is ACM Georgia LLC with 400 employees.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2621,13 +2657,13 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Thermal Ceramics Inc. | Vehicle Assembly | Manufacturing Plant  
-Freudenberg-NOK | Thermal Management | Manufacturing Plant</t>
+          <t>Thermal Ceramics Inc. | Vehicle Assembly | Manufacturing Plant
+Vista Metals Corp. | EV and ICE component manufacturing | Manufacturing plant</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
@@ -2637,16 +2673,16 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>30.76923076923077</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="42">
@@ -2673,10 +2709,10 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fouts Brothers Fire Equipment | Category: Tier 1/2 | Industry Group: Fabricated Metal Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 630 | EV / Battery Relevant: Indirect
-Hyundai Industrial Co. | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 182 | EV / Battery Relevant: Indirect
-Hyundai MOBIS (Georgia) | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 170 | EV / Battery Relevant: Indirect
-Hyundai Transys Georgia Seating Systems | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 110 | EV / Battery Relevant: Indirect</t>
+          <t>Fouts Brothers Fire Equipment | Category: Tier 1/2 | Industry Group: Fabricated Metal Products | EV Supply Chain Role: General Automotive | Employment: 630 | EV / Battery Relevant: Indirect
+Hyundai Industrial Co. | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Employment: 182 | EV / Battery Relevant: Indirect
+Hyundai MOBIS (Georgia) | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Employment: 170 | EV / Battery Relevant: Indirect
+Hyundai Transys Georgia Seating Systems | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Employment: 110 | EV / Battery Relevant: Indirect</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2726,12 +2762,10 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>The demand for thermal management solutions in Georgia is reflected through 5 suppliers employing a total of 17960 people:
-- Freudenberg-NOK | Employment: 160
-- Hyundai Transys Georgia Powertrain | Employment: 130
-- Novelis Inc. | Employment: 200
-- Peerless-Winsmith Inc. | Employment: 160
-- ZF Gainesville LLC | Employment: 17500</t>
+          <t>The demand for thermal management solutions in Georgia is reflected through 3 suppliers, each contributing to employment as follows:
+- Freudenberg-NOK | Employment: 160 | Location: Lagrange, Troup County
+- Hyundai Transys Georgia Powertrain | Employment: 130 | Location: West Point, Troup County
+- Peerless-Winsmith Inc. | Employment: 160 | Location: Peachtree City, Fayette County</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2779,8 +2813,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>F&amp;P Georgia Manufacturing | Category: Tier 1/2 | EV / Battery Relevant: Yes
-SungEel Recycling Park Georgia | Category: Tier 2/3 | Employment: 650</t>
+          <t>No Georgia companies involved in battery recycling or second-life battery processing were listed in the provided evidence. All companies mentioned have an EV Supply Chain Role of "General Automotive" and are not relevant to battery recycling or second-life batteries according to the given data.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2826,16 +2859,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>General Automotive:
-- Bosal Industries Georgia
-- GEDIA Georgia LLC
-- Denso Manufacturing Georgia
-- Hyundai Transys Georgia Seating Systems
-- Ajin Georgia
-- ADVICS Manufacturing Georgia LLC
-- GLOVIS Georgia LLC
-Thermal Management:
-- Hyundai Transys Georgia Powertrain</t>
+          <t>Based on the provided evidence, there are no Georgia suppliers listed as playing innovation-stage roles through research, development, or prototyping activity. All companies listed have an EV Supply Chain Role of "General Automotive" and do not indicate involvement in innovation-stage activities specifically.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2885,10 +2909,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ACM Georgia LLC | Category: Tier 2/3 | Industry Group: Textile Products | EV Supply Chain Role: General Automotive | Primary OEMs: Multiple OEMs | Product / Service: Automotive floor mats made of purchased wire | Location: Covington, Henry County | Primary Facility Type: Manufacturing Plant | Employment: 400 | EV / Battery Relevant: Indirect  
-GEDIA Georgia LLC | Category: Tier 2/3 | Industry Group: Fabricated Metal Products | EV Supply Chain Role: General Automotive | Primary OEMs: Multiple OEMs | Product / Service: Automotive stampings | Location: Cumming, Forsyth County | Primary Facility Type: Manufacturing Plant | Employment: 100 | EV / Battery Relevant: Indirect  
-Hyundai Transys Georgia Seating Systems | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | EV Supply Chain Role: General Automotive | Primary OEMs: Multiple OEMs | Product / Service: Automotive electronics, resonators, capacitors, resistors, electronics and electronic parts | Location: Rome, Floyd County | Primary Facility Type: Manufacturing Plant | Employment: 110 | EV / Battery Relevant: Indirect  
-GLOVIS Georgia LLC | Category: Tier 2/3 | Industry Group: Fabricated Metal Products | EV Supply Chain Role: General Automotive | Primary OEMs: Multiple OEMs | Product / Service: Metal parts and subassemblies for the automotive industry | Location: Pooler, Chatham County | Primary Facility Type: Manufacturing Plant | Employment: 90 | EV / Battery Relevant: Indirect</t>
+          <t>Based on the provided evidence, there are no Georgia suppliers currently serving traditional OEMs and also linked to EV-native OEMs showing dual-platform supply capability. The companies listed have an "EV / Battery Relevant" status of either Indirect or No, indicating they do not specifically serve EV-native OEMs.
+- ACM Georgia LLC | Category: Tier 2/3 | Industry Group: Textile Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 400 | EV / Battery Relevant: Indirect
+- Adient | Category: Tier 2/3 | Industry Group: Textile Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 180 | EV / Battery Relevant: Indirect
+- ADVICS Manufacturing Georgia LLC | Category: Tier 2/3 | Industry Group: Textile Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 150 | EV / Battery Relevant: No
+- Ajin Georgia | Category: Tier 2/3 | Industry Group: Textile Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 143 | EV / Battery Relevant: No
+- ALBAform Inc. | Category: Tier 2/3 | Industry Group: Textile Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 130 | EV / Battery Relevant: No</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2970,7 +2996,8 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Commerce, Forsyth County:
+          <t>Georgia areas that currently lack Battery Cell or Battery Pack suppliers but have existing Tier 1 general automotive infrastructure:
+Commerce, Forsyth County:
 - Jefferson Southern Corporation (Employment: 900)
 - Joon Georgia, Inc. (Employment: 900)
 Warrenton, Warren County:
@@ -3044,9 +3071,13 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>For a new Tier 1 battery thermal management company looking to locate in Georgia, the areas with compatible upstream material suppliers include:
-- Atlanta, Fulton County | Company: Novelis Inc. | Employment: 200 | EV / Battery Relevant: Indirect | Product / Service: Acoustic and thermally effective automotive components
-- Peachtree City, Fayette County | Company: Peerless-Winsmith Inc. | Employment: 160 | EV / Battery Relevant: No | Product / Service: Thermal solutions</t>
+          <t>For a new Tier 1 battery thermal management company looking to locate in Georgia, the areas with the highest density of compatible upstream material suppliers include:
+- Richmond County (2 companies)
+- Newton County (2 companies)
+Illustrative examples from these counties:
+- Duckyang | Augusta, Richmond County | Category=Tier 2/3
+- Enchem America Inc. | Cumming, Forsyth County | Category=Tier 2/3
+Note: The provided evidence does not list all upstream material suppliers in Georgia, so the above companies are illustrative examples based on available data.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3113,9 +3144,9 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2 Georgia areas have concentrated Manufacturing Plant facilities but no EV-specific production presence, indicating potential conversion-ready industrial sites:
-- Jonesboro, Clayton County (GEDIA Georgia LLC)
-- Augusta, Richmond County (Duckyang)</t>
+          <t>2
+Company: ACM Georgia LLC | Category: Tier 2/3 | Industry Group: Textile Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 400 | Location: Covington, Henry County | EV / Battery Relevant: Indirect
+Company: Adient | Category: Tier 2/3 | Industry Group: Textile Products | EV Supply Chain Role: General Automotive | Primary Facility Type: Manufacturing Plant | Employment: 180 | Location: West Point, Chattahoochee County | EV / Battery Relevant: Indirect</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -3162,12 +3193,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>For an international battery materials company seeking a Georgia location, which areas have existing chemical manufacturing infrastructure?
-EV Supply Chain Role: Materials
-- Statesboro, Bulloch County | Company: Aurubis | Employment: 400 | EV / Battery Relevant: Indirect
-- Troup County | Companies: Aspen Aerogels (Covington, Henry County), Boogook Industries (Macon, Bibb County) | Employment: 414 + 250 = 664 | EV / Battery Relevant: No, No
-- Hartwell, Hart County | Company: SK Battery America | Employment: Not specified in evidence provided
-Note: The exact employment numbers for SK Battery America are not provided in the given evidence.</t>
+          <t>For an international battery materials company seeking a Georgia location, which areas have existing chemical manufacturing infrastructure based on the provided evidence:
+- Statesboro, Bulloch County (Aurubis)
+- Troup County (Aspen Aerogels and Aurubis)
+- Canton, Cherokee County (Blue Ridge Manufacturing) - Indirect EV / Battery Relevant
+- Hartwell, Hart County (SK Battery America)
+Note: The companies listed above are categorized under the "Materials" role in the automotive supply chain.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3213,31 +3244,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Racemark International LLC | Primary Facility Type: R&amp;D</t>
+          <t>The provided evidence does not include any companies with R&amp;D facility types in Georgia. All entries listed have Manufacturing Plant as their Primary Facility Type and do not indicate involvement specifically in EV technology development centers or R&amp;D activities.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>59.61538461538461</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
   </sheetData>
